--- a/ZonasEscolares/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>SAGRADA FAMILIA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-16.36175</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-72.19129</v>
-      </c>
-      <c r="I2" t="n">
-        <v>345</v>
-      </c>
-      <c r="J2" t="n">
-        <v>19</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-16.36175</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-72.19129</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>40097 REPUBLICA DE CANADA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-16.334877</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-72.25839000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>288</v>
-      </c>
-      <c r="J3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-16.334877</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-72.25839</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>40201 TECNICO AGROPECUARIO LA COLINA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-16.3442</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-72.177381</v>
-      </c>
-      <c r="I4" t="n">
-        <v>399</v>
-      </c>
-      <c r="J4" t="n">
-        <v>23</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-16.3442</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-72.177381</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>40230 SAN ANTONIO DEL PEDREGAL</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-16.355583</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-72.188064</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1561</v>
-      </c>
-      <c r="J5" t="n">
-        <v>66</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-16.355583</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-72.188064</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>40284 PEDRO PAULET MOSTAJO</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-16.388559</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-72.180577</v>
-      </c>
-      <c r="I6" t="n">
-        <v>326</v>
-      </c>
-      <c r="J6" t="n">
-        <v>16</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-16.388559</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-72.180577</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>40594 JUAN VELASCO A.</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-16.336328</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-72.200197</v>
-      </c>
-      <c r="I7" t="n">
-        <v>897</v>
-      </c>
-      <c r="J7" t="n">
-        <v>45</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-16.336328</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-72.200197</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>40625 CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-16.319544</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-72.239278</v>
-      </c>
-      <c r="I8" t="n">
-        <v>740</v>
-      </c>
-      <c r="J8" t="n">
-        <v>41</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-16.319544</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-72.239278</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>40629 DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-16.313314</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-72.281154</v>
-      </c>
-      <c r="I9" t="n">
-        <v>400</v>
-      </c>
-      <c r="J9" t="n">
-        <v>27</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-16.313314</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-72.281154</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>40656 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-16.315594</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-72.160926</v>
-      </c>
-      <c r="I10" t="n">
-        <v>594</v>
-      </c>
-      <c r="J10" t="n">
-        <v>31</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-16.315594</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-72.160926</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>40661 ISABEL KRIEGER BEATO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-16.302474</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-72.20351100000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>671</v>
-      </c>
-      <c r="J11" t="n">
-        <v>43</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-16.302474</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-72.203511</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>41061 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-16.350267</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-72.28175400000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>726</v>
-      </c>
-      <c r="J12" t="n">
-        <v>44</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-16.350267</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-72.281754</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>41062 DR. MARIO VARGAS LLOSA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-16.42095</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-72.229857</v>
-      </c>
-      <c r="I13" t="n">
-        <v>393</v>
-      </c>
-      <c r="J13" t="n">
-        <v>18</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-16.42095</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-72.229857</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>41502</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-16.405817</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-72.242479</v>
-      </c>
-      <c r="I14" t="n">
-        <v>229</v>
-      </c>
-      <c r="J14" t="n">
-        <v>14</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-16.405817</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-72.242479</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-16.358157</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-72.189531</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1352</v>
-      </c>
-      <c r="J15" t="n">
-        <v>63</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-16.358157</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-72.189531</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1352</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>NUESTRA SRA. DE LA PAZ</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-16.328735</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-72.26320200000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>323</v>
-      </c>
-      <c r="J16" t="n">
-        <v>15</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-16.328735</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-72.263202</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>JUSTO JUEZ</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-16.35287</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-72.18816</v>
-      </c>
-      <c r="I17" t="n">
-        <v>248</v>
-      </c>
-      <c r="J17" t="n">
-        <v>28</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-16.35287</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-72.18816</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>SANTA TERESA DE LISIEUX</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-16.339971</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-72.174312</v>
-      </c>
-      <c r="I18" t="n">
-        <v>207</v>
-      </c>
-      <c r="J18" t="n">
-        <v>16</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-16.339971</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-72.174312</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>VALORES SCHOOL</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-16.35857</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-72.18831</v>
-      </c>
-      <c r="I19" t="n">
-        <v>309</v>
-      </c>
-      <c r="J19" t="n">
-        <v>19</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-16.35857</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-72.18831</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>CIENCIAS APLICADAS</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-16.363989</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-72.192786</v>
-      </c>
-      <c r="I20" t="n">
-        <v>343</v>
-      </c>
-      <c r="J20" t="n">
-        <v>31</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-16.363989</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-72.192786</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>JOSE A. QUIÑONES GONZALES</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-16.3619</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-72.18931000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>168</v>
-      </c>
-      <c r="J21" t="n">
-        <v>12</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-16.3619</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-72.18931</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>MAXWELL SCHOOL</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-16.36067</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-72.18808</v>
-      </c>
-      <c r="I22" t="n">
-        <v>243</v>
-      </c>
-      <c r="J22" t="n">
-        <v>29</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-16.36067</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-72.18808</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>40698 SAN JUAN BAUTISTA DE MAJES</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-16.373064</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-72.198442</v>
-      </c>
-      <c r="I23" t="n">
-        <v>210</v>
-      </c>
-      <c r="J23" t="n">
-        <v>10</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-16.373064</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-72.198442</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>40201 TECNICO AGROPECUARIO LA COLINA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-16.340892</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-72.17423100000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>365</v>
-      </c>
-      <c r="J24" t="n">
-        <v>15</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-16.340892</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-72.174231</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>BELAUNDE TERRY</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-16.342191</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-72.183762</v>
-      </c>
-      <c r="I25" t="n">
-        <v>270</v>
-      </c>
-      <c r="J25" t="n">
-        <v>10</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-16.342191</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-72.183762</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>CORONEL FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-16.321544</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-72.18002</v>
-      </c>
-      <c r="I26" t="n">
-        <v>854</v>
-      </c>
-      <c r="J26" t="n">
-        <v>34</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-16.321544</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-72.18002</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>CIMAS</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-16.350991</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-72.184251</v>
-      </c>
-      <c r="I27" t="n">
-        <v>254</v>
-      </c>
-      <c r="J27" t="n">
-        <v>22</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-16.350991</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-72.184251</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>MARIA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-16.35428</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-72.18841999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>224</v>
-      </c>
-      <c r="J28" t="n">
-        <v>15</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-16.35428</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-72.18842</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>40284 PEDRO PAULET MOSTAJO</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-16.388488</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-72.178741</v>
-      </c>
-      <c r="I29" t="n">
-        <v>329</v>
-      </c>
-      <c r="J29" t="n">
-        <v>24</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-16.388488</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-72.178741</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>BLANCA VARELA GONZALES</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-16.3145</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-72.19110000000001</v>
-      </c>
-      <c r="I30" t="n">
-        <v>393</v>
-      </c>
-      <c r="J30" t="n">
-        <v>15</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-16.3145</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-72.1911</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>LOS DINAMICOS</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-16.38503</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-72.20285</v>
-      </c>
-      <c r="I31" t="n">
-        <v>334</v>
-      </c>
-      <c r="J31" t="n">
-        <v>14</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-16.38503</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-72.20285</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>MARIANO LORENZO MELGAR VALDIVIESO</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-16.330793</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-72.19410499999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>243</v>
-      </c>
-      <c r="J32" t="n">
-        <v>9</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-16.330793</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-72.194105</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>DR JUAN MANUEL GUILLEN BENAVIDES</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-16.342904</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-72.189876</v>
-      </c>
-      <c r="I33" t="n">
-        <v>382</v>
-      </c>
-      <c r="J33" t="n">
-        <v>17</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-16.342904</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-72.189876</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>RICARDO PALMA SORIANO</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-16.32469</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-72.19311</v>
-      </c>
-      <c r="I34" t="n">
-        <v>256</v>
-      </c>
-      <c r="J34" t="n">
-        <v>13</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-16.32469</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-72.19311</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>CIENCIAS</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-16.35999</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-72.1892</v>
-      </c>
-      <c r="I35" t="n">
-        <v>267</v>
-      </c>
-      <c r="J35" t="n">
-        <v>12</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-16.35999</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-72.1892</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>SAN CARLOS</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-16.36045</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-72.19092999999999</v>
-      </c>
-      <c r="I36" t="n">
-        <v>362</v>
-      </c>
-      <c r="J36" t="n">
-        <v>30</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-16.36045</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-72.19093</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>BRYCE PEDREGAL</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-16.36371</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-72.19053</v>
-      </c>
-      <c r="I37" t="n">
-        <v>187</v>
-      </c>
-      <c r="J37" t="n">
-        <v>23</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-16.36371</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-72.19053</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>MENDEL PEDREGAL</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-16.36692</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-72.19182000000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>431</v>
-      </c>
-      <c r="J38" t="n">
-        <v>30</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-16.36692</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-72.19182</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>JESUS ES EL SEÑOR MAJES</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-16.36336</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-72.19</v>
-      </c>
-      <c r="I39" t="n">
-        <v>3</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-16.36336</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-72.19</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>MARIA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-16.35426</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-72.18845</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-16.35426</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-72.18845</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>47451</t>
+          <t>541244</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAGRADA FAMILIA</t>
+          <t>MARIA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.36175</t>
+          <t>-16.35426</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-72.19129</t>
+          <t>-72.18845</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>70371</t>
+          <t>865403</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40097 REPUBLICA DE CANADA</t>
+          <t>JESUS ES EL SEÑOR MAJES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-16.334877</t>
+          <t>-16.36336</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-72.25839</t>
+          <t>-72.19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70385</t>
+          <t>546048</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40201 TECNICO AGROPECUARIO LA COLINA</t>
+          <t>40698 SAN JUAN BAUTISTA DE MAJES</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.3442</t>
+          <t>-16.373064</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-72.177381</t>
+          <t>-72.198442</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70390</t>
+          <t>571245</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40230 SAN ANTONIO DEL PEDREGAL</t>
+          <t>BELAUNDE TERRY</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.355583</t>
+          <t>-16.342191</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-72.188064</t>
+          <t>-72.183762</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,42 +749,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>70408</t>
+          <t>512270</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40284 PEDRO PAULET MOSTAJO</t>
+          <t>JOSE A. QUIÑONES GONZALES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.388559</t>
+          <t>-16.3619</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-72.180577</t>
+          <t>-72.18931</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>168</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>70470</t>
+          <t>820259</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40594 JUAN VELASCO A.</t>
+          <t>CIENCIAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.336328</t>
+          <t>-16.35999</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-72.200197</t>
+          <t>-72.1892</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70489</t>
+          <t>798734</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40625 CORAZON DE JESUS</t>
+          <t>RICARDO PALMA SORIANO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.319544</t>
+          <t>-16.32469</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-72.239278</t>
+          <t>-72.19311</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>256</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>70516</t>
+          <t>70371</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40629 DIVINO NIÑO JESUS</t>
+          <t>40097 REPUBLICA DE CANADA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.313314</t>
+          <t>-16.334877</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-72.281154</t>
+          <t>-72.25839</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70540</t>
+          <t>70615</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40656 SAN FRANCISCO DE ASIS</t>
+          <t>41502</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.315594</t>
+          <t>-16.405817</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-72.160926</t>
+          <t>-72.242479</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>70559</t>
+          <t>680857</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40661 ISABEL KRIEGER BEATO</t>
+          <t>LOS DINAMICOS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.302474</t>
+          <t>-16.38503</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-72.203511</t>
+          <t>-72.20285</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>334</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>70583</t>
+          <t>70781</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41061 JOSE ANTONIO ENCINAS</t>
+          <t>NUESTRA SRA. DE LA PAZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.350267</t>
+          <t>-16.328735</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-72.281754</t>
+          <t>-72.263202</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>323</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>70597</t>
+          <t>561675</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41062 DR. MARIO VARGAS LLOSA</t>
+          <t>40201 TECNICO AGROPECUARIO LA COLINA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-16.42095</t>
+          <t>-16.340892</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-72.229857</t>
+          <t>-72.174231</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>365</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>70615</t>
+          <t>623980</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41502</t>
+          <t>MARIA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-16.405817</t>
+          <t>-16.35428</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-72.242479</t>
+          <t>-72.18842</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>70620</t>
+          <t>680838</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ALMIRANTE MIGUEL GRAU</t>
+          <t>BLANCA VARELA GONZALES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-16.358157</t>
+          <t>-16.3145</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-72.189531</t>
+          <t>-72.1911</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>393</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70781</t>
+          <t>70408</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NUESTRA SRA. DE LA PAZ</t>
+          <t>40284 PEDRO PAULET MOSTAJO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.328735</t>
+          <t>-16.388559</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-72.263202</t>
+          <t>-72.180577</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>326</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>70804</t>
+          <t>70837</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JUSTO JUEZ</t>
+          <t>SANTA TERESA DE LISIEUX</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-16.35287</t>
+          <t>-16.339971</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-72.18816</t>
+          <t>-72.174312</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>70837</t>
+          <t>735256</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANTA TERESA DE LISIEUX</t>
+          <t>DR JUAN MANUEL GUILLEN BENAVIDES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-16.339971</t>
+          <t>-16.342904</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-72.174312</t>
+          <t>-72.189876</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>382</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>70875</t>
+          <t>70597</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VALORES SCHOOL</t>
+          <t>41062 DR. MARIO VARGAS LLOSA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.35857</t>
+          <t>-16.42095</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-72.18831</t>
+          <t>-72.229857</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>393</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71460</t>
+          <t>47451</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CIENCIAS APLICADAS</t>
+          <t>SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-16.363989</t>
+          <t>-16.36175</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-72.192786</t>
+          <t>-72.19129</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>345</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1679,42 +1679,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>512270</t>
+          <t>70875</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JOSE A. QUIÑONES GONZALES</t>
+          <t>VALORES SCHOOL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-16.3619</t>
+          <t>-16.35857</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-72.18931</t>
+          <t>-72.18831</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>309</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>513750</t>
+          <t>572886</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MAXWELL SCHOOL</t>
+          <t>CIMAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-16.36067</t>
+          <t>-16.350991</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-72.18808</t>
+          <t>-72.184251</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>546048</t>
+          <t>70385</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40698 SAN JUAN BAUTISTA DE MAJES</t>
+          <t>40201 TECNICO AGROPECUARIO LA COLINA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-16.373064</t>
+          <t>-16.3442</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-72.198442</t>
+          <t>-72.177381</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>399</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>561675</t>
+          <t>820377</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>40201 TECNICO AGROPECUARIO LA COLINA</t>
+          <t>BRYCE PEDREGAL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-16.340892</t>
+          <t>-16.36371</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-72.174231</t>
+          <t>-72.19053</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>187</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>571245</t>
+          <t>626993</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BELAUNDE TERRY</t>
+          <t>40284 PEDRO PAULET MOSTAJO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-16.342191</t>
+          <t>-16.388488</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-72.183762</t>
+          <t>-72.178741</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>571250</t>
+          <t>70516</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CORONEL FRANCISCO BOLOGNESI</t>
+          <t>40629 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-16.321544</t>
+          <t>-16.313314</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-72.18002</t>
+          <t>-72.281154</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>572886</t>
+          <t>70804</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CIMAS</t>
+          <t>JUSTO JUEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-16.350991</t>
+          <t>-16.35287</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-72.184251</t>
+          <t>-72.18816</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>623980</t>
+          <t>513750</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MARIA DE LOS ANGELES</t>
+          <t>MAXWELL SCHOOL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-16.35428</t>
+          <t>-16.36067</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-72.18842</t>
+          <t>-72.18808</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>626993</t>
+          <t>820344</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>40284 PEDRO PAULET MOSTAJO</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-16.388488</t>
+          <t>-16.36045</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-72.178741</t>
+          <t>-72.19093</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>680838</t>
+          <t>864880</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BLANCA VARELA GONZALES</t>
+          <t>MENDEL PEDREGAL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-16.3145</t>
+          <t>-16.36692</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-72.1911</t>
+          <t>-72.19182</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>431</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>680857</t>
+          <t>70540</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LOS DINAMICOS</t>
+          <t>40656 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-16.38503</t>
+          <t>-16.315594</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-72.20285</t>
+          <t>-72.160926</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>594</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>735242</t>
+          <t>71460</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MARIANO LORENZO MELGAR VALDIVIESO</t>
+          <t>CIENCIAS APLICADAS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-16.330793</t>
+          <t>-16.363989</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-72.194105</t>
+          <t>-72.192786</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>343</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>735256</t>
+          <t>571250</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DR JUAN MANUEL GUILLEN BENAVIDES</t>
+          <t>CORONEL FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-16.342904</t>
+          <t>-16.321544</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-72.189876</t>
+          <t>-72.18002</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>854</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>798734</t>
+          <t>70489</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RICARDO PALMA SORIANO</t>
+          <t>40625 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-16.32469</t>
+          <t>-16.319544</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-72.19311</t>
+          <t>-72.239278</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>740</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>820259</t>
+          <t>70559</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CIENCIAS</t>
+          <t>40661 ISABEL KRIEGER BEATO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-16.35999</t>
+          <t>-16.302474</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-72.1892</t>
+          <t>-72.203511</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>671</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>820344</t>
+          <t>70583</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>41061 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-16.36045</t>
+          <t>-16.350267</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-72.19093</t>
+          <t>-72.281754</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>726</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,42 +2671,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>820377</t>
+          <t>70470</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>BRYCE PEDREGAL</t>
+          <t>40594 JUAN VELASCO A.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-16.36371</t>
+          <t>-16.336328</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-72.19053</t>
+          <t>-72.200197</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>897</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>864880</t>
+          <t>70620</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MENDEL PEDREGAL</t>
+          <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-16.36692</t>
+          <t>-16.358157</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-72.19182</t>
+          <t>-72.189531</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2795,42 +2795,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>865403</t>
+          <t>70390</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JESUS ES EL SEÑOR MAJES</t>
+          <t>40230 SAN ANTONIO DEL PEDREGAL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-16.36336</t>
+          <t>-16.355583</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-72.19</t>
+          <t>-72.188064</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>541244</t>
+          <t>735242</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MARIA DE LOS ANGELES</t>
+          <t>MARIANO LORENZO MELGAR VALDIVIESO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-16.35426</t>
+          <t>-16.330793</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-72.18845</t>
+          <t>-72.194105</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
@@ -501,42 +501,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>541244</t>
+          <t>865403</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MARIA DE LOS ANGELES</t>
+          <t>JESUS ES EL SEÑOR MAJES</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.35426</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-72.18845</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.36336</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-72.19</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>865403</t>
+          <t>864880</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JESUS ES EL SEÑOR MAJES</t>
+          <t>MENDEL PEDREGAL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-16.36336</t>
+          <t>431</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-72.19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-16.36692</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-72.19182</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>546048</t>
+          <t>820377</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40698 SAN JUAN BAUTISTA DE MAJES</t>
+          <t>BRYCE PEDREGAL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.373064</t>
+          <t>187</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-72.198442</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-16.36371</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-72.19053</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>571245</t>
+          <t>820344</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BELAUNDE TERRY</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.342191</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-72.183762</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-16.36045</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-72.19093</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>512270</t>
+          <t>820259</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JOSE A. QUIÑONES GONZALES</t>
+          <t>CIENCIAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.3619</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-72.18931</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>-16.35999</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-72.1892</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>820259</t>
+          <t>798734</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CIENCIAS</t>
+          <t>RICARDO PALMA SORIANO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.35999</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-72.1892</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-16.32469</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-72.19311</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>798734</t>
+          <t>735256</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RICARDO PALMA SORIANO</t>
+          <t>DR JUAN MANUEL GUILLEN BENAVIDES</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.32469</t>
+          <t>382</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-72.19311</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>-16.342904</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-72.189876</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>70371</t>
+          <t>735242</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40097 REPUBLICA DE CANADA</t>
+          <t>MARIANO LORENZO MELGAR VALDIVIESO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.334877</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-72.25839</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>-16.330793</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-72.194105</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70615</t>
+          <t>680857</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41502</t>
+          <t>LOS DINAMICOS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.405817</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-72.242479</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-16.38503</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-72.20285</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>680857</t>
+          <t>680838</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LOS DINAMICOS</t>
+          <t>BLANCA VARELA GONZALES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.38503</t>
+          <t>393</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-72.20285</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>-16.3145</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-72.1911</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>70781</t>
+          <t>626993</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NUESTRA SRA. DE LA PAZ</t>
+          <t>40284 PEDRO PAULET MOSTAJO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.328735</t>
+          <t>329</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-72.263202</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>-16.388488</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-72.178741</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,42 +1183,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>561675</t>
+          <t>623980</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40201 TECNICO AGROPECUARIO LA COLINA</t>
+          <t>MARIA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-16.340892</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-72.174231</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>-16.35428</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-72.18842</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>623980</t>
+          <t>572886</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MARIA DE LOS ANGELES</t>
+          <t>CIMAS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-16.35428</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-72.18842</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-16.350991</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-72.184251</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>680838</t>
+          <t>571250</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BLANCA VARELA GONZALES</t>
+          <t>CORONEL FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-16.3145</t>
+          <t>854</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-72.1911</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>-16.321544</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-72.18002</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70408</t>
+          <t>571245</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40284 PEDRO PAULET MOSTAJO</t>
+          <t>BELAUNDE TERRY</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.388559</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-72.180577</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>-16.342191</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-72.183762</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>70837</t>
+          <t>561675</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANTA TERESA DE LISIEUX</t>
+          <t>40201 TECNICO AGROPECUARIO LA COLINA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-16.339971</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-72.174312</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>-16.340892</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-72.174231</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>735256</t>
+          <t>546048</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DR JUAN MANUEL GUILLEN BENAVIDES</t>
+          <t>40698 SAN JUAN BAUTISTA DE MAJES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-16.342904</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-72.189876</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>-16.373064</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-72.198442</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>70597</t>
+          <t>541244</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41062 DR. MARIO VARGAS LLOSA</t>
+          <t>MARIA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.42095</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-72.229857</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>-16.35426</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-72.18845</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>47451</t>
+          <t>513750</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SAGRADA FAMILIA</t>
+          <t>MAXWELL SCHOOL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-16.36175</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-72.19129</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>-16.36067</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-72.18808</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,42 +1679,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>70875</t>
+          <t>512270</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VALORES SCHOOL</t>
+          <t>JOSE A. QUIÑONES GONZALES</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-16.35857</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-72.18831</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>-16.3619</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-72.18931</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>572886</t>
+          <t>071460</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CIMAS</t>
+          <t>CIENCIAS APLICADAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-16.350991</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-72.184251</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-16.363989</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-72.192786</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>70385</t>
+          <t>070875</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40201 TECNICO AGROPECUARIO LA COLINA</t>
+          <t>VALORES SCHOOL</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-16.3442</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-72.177381</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>-16.35857</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-72.18831</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,42 +1865,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>820377</t>
+          <t>070837</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BRYCE PEDREGAL</t>
+          <t>SANTA TERESA DE LISIEUX</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-16.36371</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-72.19053</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>-16.339971</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-72.174312</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>626993</t>
+          <t>070804</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>40284 PEDRO PAULET MOSTAJO</t>
+          <t>JUSTO JUEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-16.388488</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-72.178741</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>-16.35287</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-72.18816</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>70516</t>
+          <t>070781</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>40629 DIVINO NIÑO JESUS</t>
+          <t>NUESTRA SRA. DE LA PAZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-16.313314</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-72.281154</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>-16.328735</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-72.263202</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>70804</t>
+          <t>070620</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JUSTO JUEZ</t>
+          <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-16.35287</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-72.18816</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-16.358157</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-72.189531</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>513750</t>
+          <t>070615</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MAXWELL SCHOOL</t>
+          <t>41502</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-16.36067</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-72.18808</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-16.405817</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-72.242479</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>820344</t>
+          <t>070597</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>41062 DR. MARIO VARGAS LLOSA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-16.36045</t>
+          <t>393</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-72.19093</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-16.42095</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-72.229857</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>864880</t>
+          <t>070583</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MENDEL PEDREGAL</t>
+          <t>41061 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-16.36692</t>
+          <t>726</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-72.19182</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>-16.350267</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-72.281754</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>70540</t>
+          <t>070559</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>40656 SAN FRANCISCO DE ASIS</t>
+          <t>40661 ISABEL KRIEGER BEATO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-16.315594</t>
+          <t>671</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-72.160926</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>-16.302474</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-72.203511</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>71460</t>
+          <t>070540</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CIENCIAS APLICADAS</t>
+          <t>40656 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-16.363989</t>
+          <t>594</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-72.192786</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>-16.315594</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-72.160926</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>571250</t>
+          <t>070516</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CORONEL FRANCISCO BOLOGNESI</t>
+          <t>40629 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-16.321544</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-72.18002</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>-16.313314</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-72.281154</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>70489</t>
+          <t>070489</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2495,22 +2495,22 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>-16.319544</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>-72.239278</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>70559</t>
+          <t>070470</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>40661 ISABEL KRIEGER BEATO</t>
+          <t>40594 JUAN VELASCO A.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-16.302474</t>
+          <t>897</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-72.203511</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>-16.336328</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-72.200197</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>70583</t>
+          <t>070408</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>41061 JOSE ANTONIO ENCINAS</t>
+          <t>40284 PEDRO PAULET MOSTAJO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-16.350267</t>
+          <t>326</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-72.281754</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>-16.388559</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-72.180577</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>70470</t>
+          <t>070390</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>40594 JUAN VELASCO A.</t>
+          <t>40230 SAN ANTONIO DEL PEDREGAL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-16.336328</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-72.200197</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>-16.355583</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-72.188064</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>70620</t>
+          <t>070385</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ALMIRANTE MIGUEL GRAU</t>
+          <t>40201 TECNICO AGROPECUARIO LA COLINA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-16.358157</t>
+          <t>399</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-72.189531</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>-16.3442</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-72.177381</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>70390</t>
+          <t>070371</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>40230 SAN ANTONIO DEL PEDREGAL</t>
+          <t>40097 REPUBLICA DE CANADA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-16.355583</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-72.188064</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>-16.334877</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-72.25839</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>735242</t>
+          <t>047451</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MARIANO LORENZO MELGAR VALDIVIESO</t>
+          <t>SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-16.330793</t>
+          <t>345</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-72.194105</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-16.36175</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-72.19129</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
